--- a/data/trans_orig/IP1006-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1006-Clase-trans_orig.xlsx
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95826</t>
+          <t>95865</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163908</t>
+          <t>162546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197498</t>
+          <t>197515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>199282</t>
+          <t>197962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>397868</t>
+          <t>398112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100932</t>
+          <t>101075</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123680</t>
+          <t>123665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>226497</t>
+          <t>226396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>72450</t>
+          <t>72196</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>144641</t>
+          <t>144334</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,47 +2840,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>3949</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>8084</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>3949</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1686</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>8793</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>633597</t>
+          <t>633569</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>678997</t>
+          <t>678317</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>683918</t>
+          <t>684603</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,47 +2953,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1319510</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1315375</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1322088</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>99,9%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1319510</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1314666</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1321773</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86433</t>
+          <t>86146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174859</t>
+          <t>174805</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80324</t>
+          <t>81193</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168323</t>
+          <t>167535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202278</t>
+          <t>202307</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219991</t>
+          <t>220502</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>226190</t>
+          <t>226203</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>424939</t>
+          <t>424983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431181</t>
+          <t>431249</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -4774,47 +4774,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2522</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>677</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7140</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2522</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7647</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132694</t>
+          <t>132713</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139157</t>
+          <t>139150</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>281516</t>
+          <t>281356</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288323</t>
+          <t>288326</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11498</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>669313</t>
+          <t>669335</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>702003</t>
+          <t>702528</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>710661</t>
+          <t>710804</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1374225</t>
+          <t>1374704</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1384129</t>
+          <t>1383900</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72224</t>
+          <t>72147</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133773</t>
+          <t>133682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>220543</t>
+          <t>219935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>431383</t>
+          <t>430957</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>537</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129641</t>
+          <t>130740</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135654</t>
+          <t>135657</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>139970</t>
+          <t>139486</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272796</t>
+          <t>272839</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278629</t>
+          <t>278625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62554</t>
+          <t>64393</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124907</t>
+          <t>124838</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>664232</t>
+          <t>664798</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>670624</t>
+          <t>670846</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>704276</t>
+          <t>703735</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>709117</t>
+          <t>709111</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1371906</t>
+          <t>1372055</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1379305</t>
+          <t>1379279</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/IP1006-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1006-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1183,42 +1183,42 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1296,52 +1296,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3473</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3453</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4178</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>98637</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>95859</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>98637</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>95865</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162546</t>
+          <t>163271</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3218</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4112</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4637</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4695</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>201389</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>198624</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>200091</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>197515</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>197505</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>201389</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>197962</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>605</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398112</t>
+          <t>398170</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2099,102 +2099,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3966</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3435</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3624</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4906</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5014</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>126569</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>123323</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>103437</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>101075</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>100685</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,34%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>126569</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>123665</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>346</t>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>226396</t>
+          <t>226504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,107 +2437,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2674</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3048</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2928</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -2555,69 +2555,69 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>74346</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>72196</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>71696</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>95,76%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>218</t>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>144334</t>
+          <t>144214</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2785,67 +2785,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5919</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>1849</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5287</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5119</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6286</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>682503</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>678684</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>683920</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>950</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>637007</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>633569</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>638335</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>633737</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>638333</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>99,92%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1026</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>682503</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>678317</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1976</t>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1315375</t>
+          <t>1315443</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1322088</t>
+          <t>1322049</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,107 +3357,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3380</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3617</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3347</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3398</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -3470,72 +3470,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89096</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>86383</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>89096</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>86146</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174805</t>
+          <t>174856</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3813,47 +3813,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4043,107 +4043,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>685</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3012</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3432</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3080</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3560</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -4156,74 +4156,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>83520</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>81193</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>80773</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,19%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,92%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>247</t>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167535</t>
+          <t>168015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,107 +4386,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6785</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3321</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3281</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2700</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6362</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>3360</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1247</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>7451</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>3360</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>7509</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -4499,74 +4499,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>224164</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>220079</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>226196</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,01%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>204967</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>202307</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>202347</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>224164</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>220502</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>226203</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>615</t>
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>424983</t>
+          <t>425041</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431249</t>
+          <t>431245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,92 +4729,92 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2522</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7193</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>2522</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7121</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2522</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -4842,72 +4842,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>137312</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>132641</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139155</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>137312</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>132713</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>139150</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>281356</t>
+          <t>281724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288326</t>
+          <t>288325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5185,47 +5185,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2577</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10986</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1346</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4746</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4690</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2697</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>10973</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>12476</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -5528,74 +5528,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>707612</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>702515</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>710924</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>971</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>672735</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>669335</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>669391</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>707612</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>702528</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>710804</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1981</t>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1374704</t>
+          <t>1375106</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1383900</t>
+          <t>1384162</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6105,47 +6105,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6448,47 +6448,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6678,107 +6678,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4250</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>634</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3281</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3586</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -6791,72 +6791,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74794</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>71178</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>74794</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>72147</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133682</t>
+          <t>134060</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,107 +7021,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3642</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2671</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3054</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3474</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -7134,74 +7134,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>222977</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>219935</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>220906</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>641</t>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>430957</t>
+          <t>431377</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7364,72 +7364,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2073</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>537</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5454</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5539</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3602</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -7477,74 +7477,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>142462</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>138988</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>134121</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>130740</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>135657</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>130655</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>135658</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,48%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>95,93%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,61%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>142462</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>139486</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>400</t>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272839</t>
+          <t>272763</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278625</t>
+          <t>278634</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7707,107 +7707,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3723</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3432</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4157</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4074</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -7820,72 +7820,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67085</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>64102</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>94,51%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>67085</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>64393</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124838</t>
+          <t>124755</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2673</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6704</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6837</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6002</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9184</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -8163,74 +8163,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>707738</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>703707</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>709112</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1009</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>668829</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>664798</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>670846</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>664665</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>670837</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,6%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>99,9%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1014</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>707738</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>703735</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>709111</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>2023</t>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1372055</t>
+          <t>1371762</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1379279</t>
+          <t>1379300</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
